--- a/backend/services/testdata/tz_synthetic.xlsx
+++ b/backend/services/testdata/tz_synthetic.xlsx
@@ -53,7 +53,7 @@
     <t>За 2-3 дня до выхода на работу</t>
   </si>
   <si>
-    <t>Описание бота...</t>
+    <t>Что умеет этот бот...</t>
   </si>
   <si>
     <t>Да</t>
